--- a/examples/hayden_case_studies/radioactive_waste.xlsx
+++ b/examples/hayden_case_studies/radioactive_waste.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -712,29 +712,29 @@
           <t>Central Interstate Compact Commission</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>authority: Authority to accept waste and collect surcharges
 rule: Compact regulations and operating requirements
 money: Compact administrative funding and technical assistance</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>rule: Waste acceptance criteria and shipping requirements for Arka...</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>rule: Waste acceptance criteria and shipping requirements for Kans...</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>rule: Waste acceptance criteria and shipping requirements for Loui...</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>rule: Waste acceptance criteria and shipping requirements for Okla...</t>
         </is>
@@ -752,7 +752,7 @@
           <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>rule: Facility licensing requirements and safety standards</t>
         </is>
@@ -761,7 +761,7 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>authority: Federal authorization for interstate compact operations
 rule: Federal regulations for LLRW disposal and licensing</t>
@@ -847,7 +847,7 @@
           <t>Nebraska Citizens</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>rule: NIMBY opposition and legal challenges to facility siting</t>
         </is>
@@ -934,37 +934,37 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Regulatory Commission</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
           <t>Central Interstate Compact Commission</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Central Compact grants Nebraska host state authority and regulatory power</t>
+          <t>Federal NRC authorizes and oversees Central Compact operations</t>
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Central Compact regulates Kansas waste management</t>
+          <t>Federal NRC regulates Nebraska disposal facility licensing and safety</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Central Compact regulates Oklahoma waste management</t>
+          <t>Central Compact regulates Louisiana waste management</t>
         </is>
       </c>
       <c r="D4" s="11" t="n">
@@ -999,12 +999,12 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Central Compact regulates Louisiana waste management</t>
+          <t>Central Compact regulates Arkansas waste management</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Central Compact regulates Arkansas waste management</t>
+          <t>Central Compact regulates Oklahoma waste management</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
@@ -1034,37 +1034,37 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Kansas generate LLRW</t>
+          <t>Central Compact grants Nebraska host state authority and regulatory power</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Oklahoma generate LLRW</t>
+          <t>Central Compact regulates Kansas waste management</t>
         </is>
       </c>
       <c r="D8" s="11" t="n">
@@ -1074,41 +1074,41 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Louisiana generate LLRW</t>
+          <t>Louisiana ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Arkansas generate LLRW</t>
+          <t>Arkansas ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1134,37 +1134,37 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Medical/research facilities in Kansas generate LLRW</t>
+          <t>Oklahoma ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Medical/research facilities in Oklahoma generate LLRW</t>
+          <t>Nebraska provides disposal capacity to Louisiana</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
@@ -1174,17 +1174,17 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Medical/research facilities in Louisiana generate LLRW</t>
+          <t>Nebraska provides disposal capacity to Arkansas</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
@@ -1194,17 +1194,17 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Medical/research facilities in Arkansas generate LLRW</t>
+          <t>Nebraska provides disposal capacity to Oklahoma</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
@@ -1234,37 +1234,37 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nebraska provides disposal capacity to Oklahoma</t>
+          <t>Kansas ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Environmental Advocacy Groups</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nebraska provides disposal capacity to Louisiana</t>
+          <t>Environmental groups provide public input to NRC regulatory process</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
@@ -1274,17 +1274,17 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Environmental Advocacy Groups</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nebraska provides disposal capacity to Arkansas</t>
+          <t>Environmental groups provide instrumental safety analysis and monitoring (INSTRUMENTAL VALUE)</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
@@ -1294,17 +1294,17 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Environmental Advocacy Groups</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Environmental groups provide instrumental safety analysis and monitoring (INSTRUMENTAL VALUE)</t>
+          <t>Nuclear utilities in Louisiana generate LLRW</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
@@ -1314,17 +1314,17 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Environmental Advocacy Groups</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Environmental groups provide public input to NRC regulatory process</t>
+          <t>Nuclear utilities in Arkansas generate LLRW</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
@@ -1334,57 +1334,57 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kansas ships LLRW to Nebraska disposal facility</t>
+          <t>Nuclear utilities in Oklahoma generate LLRW</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Federal NRC authorizes and oversees Central Compact operations</t>
+          <t>Nuclear utilities in Kansas generate LLRW</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Medical &amp; Research Facilities</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Federal NRC regulates Nebraska disposal facility licensing and safety</t>
+          <t>Medical/research facilities in Louisiana generate LLRW</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
@@ -1394,61 +1394,61 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Medical &amp; Research Facilities</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Oklahoma ships LLRW to Nebraska disposal facility</t>
+          <t>Medical/research facilities in Arkansas generate LLRW</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Medical &amp; Research Facilities</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Louisiana ships LLRW to Nebraska disposal facility</t>
+          <t>Medical/research facilities in Oklahoma generate LLRW</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Medical &amp; Research Facilities</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Arkansas ships LLRW to Nebraska disposal facility</t>
+          <t>Medical/research facilities in Kansas generate LLRW</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1526,14 +1526,14 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Regulatory Commission</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
           <t>Central Interstate Compact Commission</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
           <t>authority</t>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Authority to accept waste and collect surcharges</t>
+          <t>Federal authorization for interstate compact operations</t>
         </is>
       </c>
       <c r="E2" s="12" t="n"/>
@@ -1555,14 +1555,14 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Regulatory Commission</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
           <t>Central Interstate Compact Commission</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
           <t>rule</t>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Compact regulations and operating requirements</t>
+          <t>Federal regulations for LLRW disposal and licensing</t>
         </is>
       </c>
       <c r="E3" s="12" t="n"/>
@@ -1578,13 +1578,13 @@
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="12" t="n"/>
       <c r="I3" s="12" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -1594,30 +1594,20 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Compact administrative funding and technical assistance</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
+          <t>Facility licensing requirements and safety standards</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
       <c r="H4" s="12" t="n"/>
       <c r="I4" s="12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1628,7 +1618,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1638,7 +1628,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Kansas</t>
+          <t>Waste acceptance criteria and shipping requirements for Louisiana</t>
         </is>
       </c>
       <c r="E5" s="12" t="n"/>
@@ -1657,7 +1647,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1667,7 +1657,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Oklahoma</t>
+          <t>Waste acceptance criteria and shipping requirements for Arkansas</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
@@ -1686,7 +1676,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1696,7 +1686,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Louisiana</t>
+          <t>Waste acceptance criteria and shipping requirements for Oklahoma</t>
         </is>
       </c>
       <c r="E7" s="12" t="n"/>
@@ -1715,17 +1705,17 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>authority</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Arkansas</t>
+          <t>Authority to accept waste and collect surcharges</t>
         </is>
       </c>
       <c r="E8" s="12" t="n"/>
@@ -1733,135 +1723,115 @@
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Kansas</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>6400</v>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>Compact regulations and operating requirements</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Oklahoma</t>
+          <t>Compact administrative funding and technical assistance</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>8000</v>
+        <v>500000</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>cubic feet/year</t>
+          <t>USD/year</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Louisiana</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>Waste acceptance criteria and shipping requirements for Kansas</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1871,11 +1841,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Arkansas</t>
+          <t>Low-level radioactive waste shipments from Louisiana</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>9600</v>
+        <v>15000</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1887,15 +1857,17 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H12" s="12" t="n"/>
+      <c r="H12" s="12" t="n">
+        <v>18000</v>
+      </c>
       <c r="I12" s="12" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Nebraska Citizens</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1905,17 +1877,27 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>NIMBY opposition and legal challenges to facility siting</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+          <t>Disposal fees and surcharges from Louisiana</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n">
         <v>0.95</v>
@@ -1924,12 +1906,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1939,11 +1921,11 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Medical and research LLRW from Kansas facilities</t>
+          <t>Low-level radioactive waste shipments from Arkansas</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1600</v>
+        <v>12000</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1955,98 +1937,90 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n"/>
+      <c r="H14" s="12" t="n">
+        <v>14400</v>
+      </c>
       <c r="I14" s="12" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Medical and research LLRW from Oklahoma facilities</t>
+          <t>Disposal fees and surcharges from Arkansas</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>2000</v>
+        <v>2400000</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>cubic feet/year</t>
+          <t>USD/year</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Nebraska Citizens</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Medical and research LLRW from Louisiana facilities</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>NIMBY opposition and legal challenges to facility siting</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Medical &amp; Research Facilities</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2056,11 +2030,11 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Medical and research LLRW from Arkansas facilities</t>
+          <t>Low-level radioactive waste shipments from Oklahoma</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2400</v>
+        <v>10000</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -2072,48 +2046,50 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H17" s="12" t="n"/>
+      <c r="H17" s="12" t="n">
+        <v>12000</v>
+      </c>
       <c r="I17" s="12" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Kansas waste</t>
+          <t>Disposal fees and surcharges from Oklahoma</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>8000</v>
+        <v>2000000</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>cubic feet/year</t>
+          <t>USD/year</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="19">
@@ -2124,7 +2100,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2134,11 +2110,11 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Oklahoma waste</t>
+          <t>Guaranteed disposal capacity for Louisiana waste</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -2163,7 +2139,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -2173,11 +2149,11 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Louisiana waste</t>
+          <t>Guaranteed disposal capacity for Arkansas waste</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2178,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2212,11 +2188,11 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Arkansas waste</t>
+          <t>Guaranteed disposal capacity for Oklahoma waste</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -2236,27 +2212,37 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Environmental Advocacy Groups</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>information</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Technical analysis and safety monitoring recommendations</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+          <t>Guaranteed disposal capacity for Kansas waste</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n">
         <v>0.85</v>
@@ -2265,30 +2251,42 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Environmental Advocacy Groups</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>information</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Public comments and technical review of NRC regulations</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="12" t="n"/>
+          <t>Low-level radioactive waste shipments from Kansas</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>9600</v>
+      </c>
       <c r="I23" s="12" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -2304,92 +2302,80 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Kansas</t>
+          <t>Disposal fees and surcharges from Kansas</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>8000</v>
+        <v>1600000</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>cubic feet/year</t>
+          <t>USD/year</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>9600</v>
-      </c>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Environmental Advocacy Groups</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>information</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Kansas</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
+          <t>Public comments and technical review of NRC regulations</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Environmental Advocacy Groups</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>authority</t>
+          <t>information</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Federal authorization for interstate compact operations</t>
+          <t>Technical analysis and safety monitoring recommendations</t>
         </is>
       </c>
       <c r="E26" s="12" t="n"/>
@@ -2397,78 +2383,98 @@
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Federal regulations for LLRW disposal and licensing</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
+          <t>Nuclear power plant LLRW requiring disposal from Louisiana</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Facility licensing requirements and safety standards</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
+          <t>Nuclear power plant LLRW requiring disposal from Arkansas</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>9600</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="H28" s="12" t="n"/>
       <c r="I28" s="12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Power Utilities</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
           <t>Oklahoma</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
           <t>pollution</t>
@@ -2476,11 +2482,11 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Oklahoma</t>
+          <t>Nuclear power plant LLRW requiring disposal from Oklahoma</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -2492,63 +2498,61 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>12000</v>
-      </c>
+      <c r="H29" s="12" t="n"/>
       <c r="I29" s="12" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Oklahoma</t>
+          <t>Nuclear power plant LLRW requiring disposal from Kansas</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>2000000</v>
+        <v>6400</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>USD/year</t>
+          <t>cubic feet/year</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
+          <t>Medical &amp; Research Facilities</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
           <t>Louisiana</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
           <t>pollution</t>
@@ -2556,11 +2560,11 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Louisiana</t>
+          <t>Medical and research LLRW from Louisiana facilities</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -2572,61 +2576,59 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H31" s="12" t="n">
-        <v>18000</v>
-      </c>
+      <c r="H31" s="12" t="n"/>
       <c r="I31" s="12" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Medical &amp; Research Facilities</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Louisiana</t>
+          <t>Medical and research LLRW from Arkansas facilities</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>3000000</v>
+        <v>2400</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>USD/year</t>
+          <t>cubic feet/year</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Medical &amp; Research Facilities</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2636,11 +2638,11 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Arkansas</t>
+          <t>Medical and research LLRW from Oklahoma facilities</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -2652,50 +2654,48 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>14400</v>
-      </c>
+      <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Medical &amp; Research Facilities</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Arkansas</t>
+          <t>Medical and research LLRW from Kansas facilities</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>2400000</v>
+        <v>1600</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>USD/year</t>
+          <t>cubic feet/year</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>

--- a/examples/hayden_case_studies/radioactive_waste.xlsx
+++ b/examples/hayden_case_studies/radioactive_waste.xlsx
@@ -53,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F4B084"/>
+        <bgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,8 +71,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B084"/>
-        <bgColor rgb="00F4B084"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -761,7 +761,7 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>authority: Federal authorization for interstate compact operations
 rule: Federal regulations for LLRW disposal and licensing</t>
@@ -780,22 +780,22 @@
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>pollution: Nuclear power plant LLRW requiring disposal from Arkansas</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>pollution: Nuclear power plant LLRW requiring disposal from Kansas</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>pollution: Nuclear power plant LLRW requiring disposal from Louisiana</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>pollution: Nuclear power plant LLRW requiring disposal from Oklahoma</t>
         </is>
@@ -814,22 +814,22 @@
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>pollution: Medical and research LLRW from Arkansas facilities</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>pollution: Medical and research LLRW from Kansas facilities</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>pollution: Medical and research LLRW from Louisiana facilities</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>pollution: Medical and research LLRW from Oklahoma facilities</t>
         </is>
@@ -934,17 +934,17 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Federal NRC authorizes and oversees Central Compact operations</t>
+          <t>Louisiana ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D2" s="11" t="n">
@@ -954,7 +954,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -964,11 +964,11 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Federal NRC regulates Nebraska disposal facility licensing and safety</t>
+          <t>Kansas ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -999,12 +999,12 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Central Compact regulates Arkansas waste management</t>
+          <t>Central Compact regulates Kansas waste management</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Central Compact regulates Oklahoma waste management</t>
+          <t>Central Compact regulates Arkansas waste management</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Central Compact regulates Kansas waste management</t>
+          <t>Central Compact regulates Oklahoma waste management</t>
         </is>
       </c>
       <c r="D8" s="11" t="n">
@@ -1074,57 +1074,57 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Power Utilities</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
           <t>Louisiana</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Louisiana ships LLRW to Nebraska disposal facility</t>
+          <t>Nuclear utilities in Louisiana generate LLRW</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Arkansas ships LLRW to Nebraska disposal facility</t>
+          <t>Nuclear utilities in Kansas generate LLRW</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Nebraska Citizens</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nebraska citizens oppose LLRW facility through political and legal resistance (CEREMONIAL VALUE)</t>
+          <t>Nuclear utilities in Arkansas generate LLRW</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
@@ -1134,77 +1134,77 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Power Utilities</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
           <t>Oklahoma</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Oklahoma ships LLRW to Nebraska disposal facility</t>
+          <t>Nuclear utilities in Oklahoma generate LLRW</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nebraska provides disposal capacity to Louisiana</t>
+          <t>Arkansas ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nebraska provides disposal capacity to Arkansas</t>
+          <t>Federal NRC authorizes and oversees Central Compact operations</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nebraska provides disposal capacity to Oklahoma</t>
+          <t>Federal NRC regulates Nebraska disposal facility licensing and safety</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nebraska provides disposal capacity to Kansas</t>
+          <t>Nebraska provides disposal capacity to Louisiana</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
@@ -1234,37 +1234,37 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>Nebraska (Host State)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Kansas ships LLRW to Nebraska disposal facility</t>
+          <t>Nebraska provides disposal capacity to Kansas</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Environmental Advocacy Groups</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Environmental groups provide public input to NRC regulatory process</t>
+          <t>Nebraska provides disposal capacity to Arkansas</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
@@ -1274,17 +1274,17 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Environmental Advocacy Groups</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Environmental groups provide instrumental safety analysis and monitoring (INSTRUMENTAL VALUE)</t>
+          <t>Nebraska provides disposal capacity to Oklahoma</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
@@ -1294,17 +1294,17 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Environmental Advocacy Groups</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Louisiana generate LLRW</t>
+          <t>Environmental groups provide public input to NRC regulatory process</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
@@ -1314,17 +1314,17 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Environmental Advocacy Groups</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Arkansas generate LLRW</t>
+          <t>Environmental groups provide instrumental safety analysis and monitoring (INSTRUMENTAL VALUE)</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
@@ -1334,17 +1334,17 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Nebraska Citizens</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Oklahoma generate LLRW</t>
+          <t>Nebraska citizens oppose LLRW facility through political and legal resistance (CEREMONIAL VALUE)</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
@@ -1354,21 +1354,21 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nuclear utilities in Kansas generate LLRW</t>
+          <t>Oklahoma ships LLRW to Nebraska disposal facility</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Medical/research facilities in Arkansas generate LLRW</t>
+          <t>Medical/research facilities in Kansas generate LLRW</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Medical/research facilities in Oklahoma generate LLRW</t>
+          <t>Medical/research facilities in Arkansas generate LLRW</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Medical/research facilities in Kansas generate LLRW</t>
+          <t>Medical/research facilities in Oklahoma generate LLRW</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
@@ -1526,65 +1526,87 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>authority</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Federal authorization for interstate compact operations</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="12" t="n"/>
+          <t>Low-level radioactive waste shipments from Louisiana</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>18000</v>
+      </c>
       <c r="I2" s="12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Federal regulations for LLRW disposal and licensing</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
+          <t>Disposal fees and surcharges from Louisiana</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="H3" s="12" t="n"/>
       <c r="I3" s="12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -1594,46 +1616,68 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Facility licensing requirements and safety standards</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="12" t="n"/>
+          <t>Low-level radioactive waste shipments from Kansas</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>9600</v>
+      </c>
       <c r="I4" s="12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Central Interstate Compact Commission</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Louisiana</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
+          <t>Disposal fees and surcharges from Kansas</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n">
         <v>0.95</v>
@@ -1647,7 +1691,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1657,7 +1701,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Arkansas</t>
+          <t>Waste acceptance criteria and shipping requirements for Louisiana</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
@@ -1676,7 +1720,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1686,7 +1730,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Oklahoma</t>
+          <t>Waste acceptance criteria and shipping requirements for Kansas</t>
         </is>
       </c>
       <c r="E7" s="12" t="n"/>
@@ -1705,17 +1749,17 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>authority</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Authority to accept waste and collect surcharges</t>
+          <t>Waste acceptance criteria and shipping requirements for Arkansas</t>
         </is>
       </c>
       <c r="E8" s="12" t="n"/>
@@ -1723,7 +1767,7 @@
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="9">
@@ -1739,12 +1783,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>authority</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Compact regulations and operating requirements</t>
+          <t>Authority to accept waste and collect surcharges</t>
         </is>
       </c>
       <c r="E9" s="12" t="n"/>
@@ -1752,7 +1796,7 @@
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1768,30 +1812,20 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Compact administrative funding and technical assistance</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>USD/year</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
+          <t>Compact regulations and operating requirements</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="11">
@@ -1802,116 +1836,114 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Waste acceptance criteria and shipping requirements for Kansas</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
+          <t>Compact administrative funding and technical assistance</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>USD/year</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Louisiana</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>18000</v>
-      </c>
+          <t>Waste acceptance criteria and shipping requirements for Oklahoma</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Power Utilities</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
           <t>Louisiana</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Louisiana</t>
+          <t>Nuclear power plant LLRW requiring disposal from Louisiana</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3000000</v>
+        <v>12000</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>USD/year</t>
+          <t>cubic feet/year</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1921,11 +1953,11 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Arkansas</t>
+          <t>Nuclear power plant LLRW requiring disposal from Kansas</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>12000</v>
+        <v>6400</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1937,85 +1969,93 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n">
-        <v>14400</v>
-      </c>
+      <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>Nuclear Power Utilities</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
           <t>Arkansas</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Arkansas</t>
+          <t>Nuclear power plant LLRW requiring disposal from Arkansas</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>2400000</v>
+        <v>9600</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>USD/year</t>
+          <t>cubic feet/year</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Nebraska Citizens</t>
+          <t>Nuclear Power Utilities</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NIMBY opposition and legal challenges to facility siting</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+          <t>Nuclear power plant LLRW requiring disposal from Oklahoma</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -2030,11 +2070,11 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Oklahoma</t>
+          <t>Low-level radioactive waste shipments from Arkansas</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -2047,7 +2087,7 @@
         </is>
       </c>
       <c r="H17" s="12" t="n">
-        <v>12000</v>
+        <v>14400</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0.9</v>
@@ -2056,7 +2096,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2071,11 +2111,11 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Oklahoma</t>
+          <t>Disposal fees and surcharges from Arkansas</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2000000</v>
+        <v>2400000</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -2095,118 +2135,88 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>authority</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Louisiana waste</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>Federal authorization for interstate compact operations</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Central Interstate Compact Commission</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Arkansas waste</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>Federal regulations for LLRW disposal and licensing</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Oklahoma waste</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>Facility licensing requirements and safety standards</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2217,7 +2227,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2227,11 +2237,11 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed disposal capacity for Kansas waste</t>
+          <t>Guaranteed disposal capacity for Louisiana waste</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -2251,22 +2261,22 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>Nebraska (Host State)</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Nebraska (Host State)</t>
-        </is>
-      </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Low-level radioactive waste shipments from Kansas</t>
+          <t>Guaranteed disposal capacity for Kansas waste</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
@@ -2282,79 +2292,87 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>9600</v>
-      </c>
+      <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Disposal fees and surcharges from Kansas</t>
+          <t>Guaranteed disposal capacity for Arkansas waste</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1600000</v>
+        <v>12000</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>USD/year</t>
+          <t>cubic feet/year</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Environmental Advocacy Groups</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Regulatory Commission</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>information</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Public comments and technical review of NRC regulations</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
+          <t>Guaranteed disposal capacity for Oklahoma waste</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>cubic feet/year</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="26">
@@ -2365,7 +2383,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Nebraska (Host State)</t>
+          <t>Nuclear Regulatory Commission</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2375,7 +2393,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Technical analysis and safety monitoring recommendations</t>
+          <t>Public comments and technical review of NRC regulations</t>
         </is>
       </c>
       <c r="E26" s="12" t="n"/>
@@ -2383,96 +2401,76 @@
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Environmental Advocacy Groups</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>information</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Louisiana</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>Technical analysis and safety monitoring recommendations</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Nebraska Citizens</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Arkansas</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>9600</v>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>cubic feet/year</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
+          <t>NIMBY opposition and legal challenges to facility siting</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
       <c r="H28" s="12" t="n"/>
       <c r="I28" s="12" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2482,11 +2480,11 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Oklahoma</t>
+          <t>Low-level radioactive waste shipments from Oklahoma</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -2498,48 +2496,50 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H29" s="12" t="n"/>
+      <c r="H29" s="12" t="n">
+        <v>12000</v>
+      </c>
       <c r="I29" s="12" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Nuclear Power Utilities</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Nebraska (Host State)</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Nuclear power plant LLRW requiring disposal from Kansas</t>
+          <t>Disposal fees and surcharges from Oklahoma</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>6400</v>
+        <v>2000000</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>cubic feet/year</t>
+          <t>USD/year</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="31">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2599,11 +2599,11 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Medical and research LLRW from Arkansas facilities</t>
+          <t>Medical and research LLRW from Kansas facilities</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2638,11 +2638,11 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Medical and research LLRW from Oklahoma facilities</t>
+          <t>Medical and research LLRW from Arkansas facilities</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2677,11 +2677,11 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Medical and research LLRW from Kansas facilities</t>
+          <t>Medical and research LLRW from Oklahoma facilities</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
